--- a/data/trans_dic/P32E$amigos_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P32E$amigos_2023-Estudios-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, realiza el atracón de alcohol en casa de amistades/familiares</t>
+          <t>Población que, al menos, realiza el atracón de alcohol en casa de amistades/familiares (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,8; 35,23</t>
+          <t>6,85; 36,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,02; 31,07</t>
+          <t>5,45; 29,67</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>15,85; 38,82</t>
+          <t>15,36; 35,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,57; 39,21</t>
+          <t>7,06; 38,24</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14,94; 34,21</t>
+          <t>16,19; 35,03</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,92; 49,31</t>
+          <t>8,81; 48,29</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,12; 48,4</t>
+          <t>10,33; 52,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13,4; 41,18</t>
+          <t>13,18; 41,06</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16,0; 32,65</t>
+          <t>16,21; 32,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,95; 34,85</t>
+          <t>10,94; 35,14</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16,81; 29,59</t>
+          <t>16,57; 30,02</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, realiza el atracón de alcohol en casa de amistades/familiares</t>
+          <t>Población que, al menos, realiza el atracón de alcohol en casa de amistades/familiares (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1842; 9544</t>
+          <t>1854; 9769</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 1033</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1929; 9964</t>
+          <t>1747; 9514</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14521; 35558</t>
+          <t>14072; 32702</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1737; 8999</t>
+          <t>1619; 8776</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17117; 39179</t>
+          <t>18545; 40120</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2001; 12461</t>
+          <t>2226; 12202</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2646; 12659</t>
+          <t>2700; 13599</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6888; 21175</t>
+          <t>6776; 21114</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>23035; 46999</t>
+          <t>23340; 47246</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6463; 18847</t>
+          <t>5915; 19003</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>33296; 58602</t>
+          <t>32805; 59452</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P32E$amigos_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P32E$amigos_2023-Estudios-trans_dic.xlsx
@@ -549,7 +549,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -559,7 +559,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>14,27%</t>
         </is>
       </c>
     </row>
@@ -572,7 +572,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,85; 36,06</t>
+          <t>6,66; 32,99</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -582,7 +582,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,45; 29,67</t>
+          <t>5,41; 29,07</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>25,1%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>15,36; 35,7</t>
+          <t>15,41; 37,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,06; 38,24</t>
+          <t>10,58; 46,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16,19; 35,03</t>
+          <t>16,27; 35,09</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>25,98%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,81; 48,29</t>
+          <t>8,19; 50,05</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,33; 52,0</t>
+          <t>11,57; 50,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13,18; 41,06</t>
+          <t>14,81; 42,56</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>23,62%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16,21; 32,82</t>
+          <t>15,96; 32,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,94; 35,14</t>
+          <t>12,72; 36,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16,57; 30,02</t>
+          <t>17,93; 31,29</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4844</t>
+          <t>4992</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4844</t>
+          <t>4992</t>
         </is>
       </c>
     </row>
@@ -879,7 +879,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1854; 9769</t>
+          <t>1941; 9621</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1747; 9514</t>
+          <t>1893; 10174</t>
         </is>
       </c>
     </row>
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>22561</t>
+          <t>26644</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4462</t>
+          <t>7136</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>27023</t>
+          <t>33780</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14072; 32702</t>
+          <t>16110; 39717</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1619; 8776</t>
+          <t>3181; 13831</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18545; 40120</t>
+          <t>21899; 47233</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6031</t>
+          <t>6511</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7271</t>
+          <t>7646</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13302</t>
+          <t>14157</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2226; 12202</t>
+          <t>2205; 13473</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2700; 13599</t>
+          <t>3191; 14027</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6776; 21114</t>
+          <t>8072; 23193</t>
         </is>
       </c>
     </row>
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>33436</t>
+          <t>38147</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>11733</t>
+          <t>14782</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>45169</t>
+          <t>52929</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>23340; 47246</t>
+          <t>25640; 52483</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5915; 19003</t>
+          <t>8074; 22969</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>32805; 59452</t>
+          <t>40183; 70107</t>
         </is>
       </c>
     </row>
